--- a/НИР_ЭДО_7стран_и_практика/05_Матрицы/Анализ_судебной_практики_ЭДО_в_ОТ.xlsx
+++ b/НИР_ЭДО_7стран_и_практика/05_Матрицы/Анализ_судебной_практики_ЭДО_в_ОТ.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -598,6 +598,7 @@
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -638,7 +639,12 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Ссылка</t>
+          <t>Ссылка 1 (проверить)</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Ссылка 2 (проверить)</t>
         </is>
       </c>
     </row>
@@ -683,6 +689,7 @@
           <t>https://www.bundesarbeitsgericht.de/entscheidung/1-abr-104-09/</t>
         </is>
       </c>
+      <c r="I2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -725,6 +732,11 @@
           <t>https://www.mintrud.gov.by/uploads/files/MTiSZ-175-po-sost.-na-02.09.2024.pdf</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>https://zakony-by.com/hozyajstvennyj_protsessualnyj_kodeks_rb/84.htm</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="92" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -767,6 +779,11 @@
           <t>https://www.lexology.com/library/detail.aspx?g=123a20c5-c0a7-425d-8c37-c9892c70dc93</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prlegal.rs/electronic-signing-of-documents-in-serbia-novelties-in-signing-of-financial-statements-for-business-registers-agency/</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="92" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -809,6 +826,11 @@
           <t>https://www.boe.es/buscar/act.php?id=BOE-A-1995-24292</t>
         </is>
       </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>https://lex.ahk.es/actualidad-juridica/puede-la-empresa-emplear-la-firma-electronica-en-el-ambito-laboral</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="92" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -851,6 +873,7 @@
           <t>https://www.bailii.org/ie/cases/IEHC/2024/2024IEHC167.html</t>
         </is>
       </c>
+      <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="92" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -893,6 +916,11 @@
           <t>https://ogletree.fr/publications/od-flash-resiliation-judiciaire-du-contrat-de-travail-et-accident-du-travail-charge-de-la-preuve-en-cas-de-manquement-de-lemployeur-aux-regles-de-prevention-et-de-securite/</t>
         </is>
       </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/av/fr/avocats/eclairages/2023/01/valeur-juridique-de-la-signature-numerisee.html</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="92" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -935,6 +963,11 @@
           <t>https://sheriahub.com/cases/ke/caselaw/bigot-flowers-kenya-ltd-v-cheboswony-employment-and-labour-relations-appeal-10of-2018-2022-keelrc-3772-klr-10may-2022-judgment.pdf</t>
         </is>
       </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>https://new.kenyalaw.org/akn/ke/act/2007/15</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="92" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -975,6 +1008,11 @@
       <c r="H9" s="6" t="inlineStr">
         <is>
           <t>https://www.consultant.ru/document/cons_doc_LAW_34683/</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_405146/</t>
         </is>
       </c>
     </row>
@@ -982,12 +1020,18 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
